--- a/Parser2/Example/Doc.xlsx
+++ b/Parser2/Example/Doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFolder\Projects\ExcelToJsonUniversalParser\Repo\Parser2\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854A2F40-D345-418B-8159-F09AAE05A642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C36C56-942F-441A-99ED-6AF245B33202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="96">
   <si>
     <t>season</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>field20</t>
+  </si>
+  <si>
+    <t>field13_2</t>
   </si>
 </sst>
 </file>
@@ -1334,6 +1337,17 @@
         <v>500</v>
       </c>
     </row>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" t="s">
+        <v>50</v>
+      </c>
+    </row>
     <row r="30" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D30" t="s">
         <v>71</v>

--- a/Parser2/Example/Doc.xlsx
+++ b/Parser2/Example/Doc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFolder\Projects\ExcelToJsonUniversalParser\Repo\Parser2\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C36C56-942F-441A-99ED-6AF245B33202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCBC3BA-0BED-4DED-9FDD-FFE9F7D1FB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AliasFuncsLvl0" sheetId="6" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="98">
   <si>
     <t>season</t>
   </si>
@@ -317,6 +317,12 @@
   </si>
   <si>
     <t>field13_2</t>
+  </si>
+  <si>
+    <t>field1_1</t>
+  </si>
+  <si>
+    <t>null</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A34CEDD6-A5B9-4B80-94E2-5A256F041AA6}">
-  <dimension ref="B1:J42"/>
+  <dimension ref="B1:J43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -1179,46 +1185,43 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.25">
@@ -1229,259 +1232,270 @@
         <v>28</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
       </c>
       <c r="F18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
         <v>48</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>49</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F22" t="s">
         <v>51</v>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D23" t="s">
+    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
         <v>62</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E24" t="s">
         <v>58</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F24" t="s">
         <v>59</v>
-      </c>
-      <c r="G23">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F24" t="s">
-        <v>63</v>
       </c>
       <c r="G24">
         <v>123</v>
       </c>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D25" t="s">
-        <v>55</v>
-      </c>
-      <c r="E25" t="s">
-        <v>56</v>
-      </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G25">
-        <v>1000</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" t="s">
+        <v>56</v>
+      </c>
+      <c r="F26" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
         <v>70</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E27" t="s">
         <v>64</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F27" t="s">
         <v>59</v>
       </c>
-      <c r="G26">
+      <c r="G27">
         <v>1234</v>
       </c>
     </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F27" t="s">
+    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="F28" t="s">
         <v>51</v>
       </c>
-      <c r="G27">
+      <c r="G28">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D28" t="s">
+    <row r="29" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
         <v>95</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E29" t="s">
         <v>27</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F29" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D30" t="s">
+    <row r="31" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
         <v>71</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E31" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D32" t="s">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
         <v>76</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E33" t="s">
         <v>72</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F33" t="s">
         <v>75</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G33" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D34" t="s">
-        <v>79</v>
-      </c>
-      <c r="E34" t="s">
-        <v>77</v>
-      </c>
-      <c r="F34" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34">
-        <v>1500</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D35" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E35" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F35" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G35">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
+        <v>83</v>
+      </c>
+      <c r="E36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" t="s">
+        <v>84</v>
+      </c>
+      <c r="G36">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
         <v>85</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E37" t="s">
         <v>87</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F37" t="s">
         <v>51</v>
       </c>
-      <c r="G36">
+      <c r="G37">
         <v>1000</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H37" s="4">
         <v>123</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I37" s="4">
         <v>1234</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J37" s="4">
         <v>12345</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F37" t="s">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F38" t="s">
         <v>89</v>
       </c>
-      <c r="G37">
+      <c r="G38">
         <v>1001</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D38" t="s">
-        <v>91</v>
-      </c>
-      <c r="E38" t="s">
-        <v>92</v>
-      </c>
-      <c r="H38" s="4">
-        <v>321</v>
-      </c>
-      <c r="I38" s="4">
-        <v>4321</v>
-      </c>
-      <c r="J38" s="4">
-        <v>54321</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
+        <v>91</v>
+      </c>
+      <c r="E39" t="s">
+        <v>92</v>
+      </c>
+      <c r="H39" s="4">
+        <v>321</v>
+      </c>
+      <c r="I39" s="4">
+        <v>4321</v>
+      </c>
+      <c r="J39" s="4">
+        <v>54321</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
         <v>94</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E40" t="s">
         <v>93</v>
       </c>
-      <c r="H39" s="4">
+      <c r="H40" s="4">
         <v>987</v>
       </c>
-      <c r="I39" s="4">
+      <c r="I40" s="4">
         <v>9876</v>
       </c>
-      <c r="J39" s="4">
+      <c r="J40" s="4">
         <v>98765</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" t="b">
         <v>0</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" t="b">
+        <v>0</v>
+      </c>
+      <c r="C43" t="s">
         <v>18</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
         <v>6</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E43" t="s">
         <v>25</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F43" t="s">
         <v>19</v>
       </c>
     </row>

--- a/Parser2/Example/Doc.xlsx
+++ b/Parser2/Example/Doc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFolder\Projects\ExcelToJsonUniversalParser\Repo\Parser2\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCBC3BA-0BED-4DED-9FDD-FFE9F7D1FB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73A7A0C-6B52-434A-B03D-58CD13D72F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AliasFuncsLvl0" sheetId="6" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="99">
   <si>
     <t>season</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>null</t>
+  </si>
+  <si>
+    <t>%arg5%</t>
   </si>
 </sst>
 </file>
@@ -694,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF3775B-0503-476A-AAFE-9E00D6710E21}">
-  <dimension ref="B1:J25"/>
+  <dimension ref="B1:J26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="51.7109375" customWidth="1"/>
@@ -927,34 +930,48 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
+    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
         <v>93</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>10</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>26</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F25" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D25" t="s">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
         <v>1</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E26" t="s">
         <v>92</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H26" t="s">
         <v>61</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I26" t="s">
         <v>60</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J26" t="s">
         <v>90</v>
       </c>
     </row>

--- a/Parser2/Example/Doc.xlsx
+++ b/Parser2/Example/Doc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFolder\Projects\ExcelToJsonUniversalParser\Repo\Parser2\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73A7A0C-6B52-434A-B03D-58CD13D72F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8797DA83-6FBD-4CB2-9C7D-0CD7E7948F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AliasFuncsLvl0" sheetId="6" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="97">
   <si>
     <t>season</t>
   </si>
@@ -298,9 +298,6 @@
     <t>workaround for float type</t>
   </si>
   <si>
-    <t>amount1</t>
-  </si>
-  <si>
     <t>%arg3%</t>
   </si>
   <si>
@@ -323,9 +320,6 @@
   </si>
   <si>
     <t>null</t>
-  </si>
-  <si>
-    <t>%arg5%</t>
   </si>
 </sst>
 </file>
@@ -697,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF3775B-0503-476A-AAFE-9E00D6710E21}">
-  <dimension ref="B1:J26"/>
+  <dimension ref="B1:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="51.7109375" customWidth="1"/>
@@ -896,7 +890,7 @@
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -927,52 +921,38 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
-        <v>93</v>
-      </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D26" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" t="s">
-        <v>61</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="I25" t="s">
         <v>60</v>
       </c>
-      <c r="J26" t="s">
-        <v>90</v>
+      <c r="J25" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -984,7 +964,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59DC35DD-449B-417F-A9B5-07ABDEE8B4C2}">
-  <dimension ref="B1:G13"/>
+  <dimension ref="B1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -993,7 +973,7 @@
     <col min="7" max="7" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>3</v>
       </c>
@@ -1012,8 +992,17 @@
       <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>67</v>
       </c>
@@ -1027,7 +1016,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>13</v>
       </c>
@@ -1038,7 +1027,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>73</v>
       </c>
@@ -1052,7 +1041,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>13</v>
       </c>
@@ -1063,7 +1052,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>78</v>
       </c>
@@ -1080,7 +1069,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>82</v>
       </c>
@@ -1202,10 +1191,10 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
         <v>96</v>
-      </c>
-      <c r="E13" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
@@ -1370,7 +1359,7 @@
     </row>
     <row r="29" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -1452,20 +1441,12 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F38" t="s">
-        <v>89</v>
-      </c>
-      <c r="G38">
-        <v>1001</v>
-      </c>
-    </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39" t="s">
         <v>91</v>
-      </c>
-      <c r="E39" t="s">
-        <v>92</v>
       </c>
       <c r="H39" s="4">
         <v>321</v>
@@ -1479,10 +1460,10 @@
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H40" s="4">
         <v>987</v>
@@ -1525,7 +1506,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{881CF64C-A86A-443D-BF50-D39123249C40}">
-  <dimension ref="B1:G29"/>
+  <dimension ref="B1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="28.5703125" customWidth="1"/>
@@ -1533,7 +1514,7 @@
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1552,8 +1533,17 @@
       <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>69</v>
       </c>
@@ -1567,7 +1557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>9</v>
       </c>
@@ -1581,7 +1571,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>1</v>
       </c>
@@ -1592,7 +1582,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>15</v>
       </c>
@@ -1603,7 +1593,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
         <v>25</v>
       </c>
@@ -1611,7 +1601,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>21</v>
       </c>
@@ -1622,7 +1612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
         <v>27</v>
       </c>
@@ -1701,6 +1691,9 @@
       </c>
       <c r="D29" t="s">
         <v>51</v>
+      </c>
+      <c r="E29" t="s">
+        <v>26</v>
       </c>
       <c r="F29">
         <v>1000</v>
@@ -1713,14 +1706,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EF7E211-A32D-4C6F-A0D1-E6C04CAD2CBB}">
-  <dimension ref="B1:G19"/>
+  <dimension ref="B1:J19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="37.42578125" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1739,8 +1732,17 @@
       <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>22</v>
       </c>
@@ -1754,7 +1756,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>42</v>
       </c>
@@ -1765,7 +1767,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>23</v>
       </c>
@@ -1779,7 +1781,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
         <v>14</v>
       </c>
@@ -1790,12 +1792,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>33</v>
       </c>
